--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -477,304 +477,304 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Humaniora</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uji Coba Tabung CNG 3 Kg Masuk Tahap Akhir</t>
+          <t>Bantuan beras 30 kg cair mulai 17 Agustus 2026, ini jadwal dan cara cek penerimanya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:58:12 +0700</t>
+          <t>Mon, 03 Aug 2026 13:27:14 +0700</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Menteri ESDM Bahlil Lahadalia menyampaikan tabung Compressed Natural Gas (CNG) 3 kilogram (kg) sebagai pengganti LPG 3 kg memasuki pengujian tahap akhir.</t>
+          <t>Pemerintah memastikan penyaluran bantuan pangan beras tahap II tahun 2026 akan dimulai pada 17 Agustus 2026. Bantuan ...</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/energi/d-8603105/uji-coba-tabung-cng-3-kg-masuk-tahap-akhir</t>
+          <t>https://www.antaranews.com/berita/5677341/bantuan-beras-30-kg-cair-mulai-17-agustus-2026-ini-jadwal-dan-cara-cek-penerimanya</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/20/cadangan-gas-raksasa-ditemukan-di-kaltim-pemerintah-genjot-energi-nasional-1776674766178_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/26/kemensos-percepat-penyaluran-bansos-pkh-dan-bpnt-2778877.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dapat Margin Fee 7%, Bulog Targetkan Untung Rp 1,14 Triliun</t>
+          <t>10 ide usaha menjelang 17 Agustus 2026 yang berpotensi laris dan menguntungkan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:32:25 +0700</t>
+          <t>Mon, 03 Aug 2026 18:16:58 +0700</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pemerintah menetapkan margin fee untuk Perum Bulog sebesar 7%</t>
+          <t>Momentum peringatan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi peluang bagi pelaku ...</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/industri/d-8603085/dapat-margin-fee-7-bulog-targetkan-untung-rp-1-14-triliun</t>
+          <t>https://www.antaranews.com/berita/5677896/10-ide-usaha-menjelang-17-agustus-2026-yang-berpotensi-laris-dan-menguntungkan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/22/f0bc228f-67f0-4a85-b1de-c8b83e0fc898_169.jpg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/02/sentra-penjualan-bendera-merah-putih-di-surabaya-020824-Ds-3.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pemerintah Kejar Rasio Wirausaha 8 Persen pada 2045</t>
+          <t>10 ide lomba 17 Agustus untuk anak PAUD dan TK yang seru, edukatif, dan mudah digelar</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 22:00:05 +0700</t>
+          <t>Mon, 03 Aug 2026 13:38:29 +0700</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UMKM makanan siap saji menjadi salah satu penggerak kewirausahaan nasional. Sejalan dengan pemerintah menargetkan rasio wirausaha mencapai 8 persen pada 2045.</t>
+          <t>Perayaan HUT ke-81 Kemerdekaan Republik Indonesia pada 17 Agustus 2026 dapat menjadi momen bagi anak usia PAUD dan TK ...</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602134/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045</t>
+          <t>https://www.antaranews.com/berita/5677368/10-ide-lomba-17-agustus-untuk-anak-paud-dan-tk-yang-seru-edukatif-dan-mudah-digelar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045-1785739243678.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/03/WhatsApp-Image-2024-08-03-at-20.37.28.jpeg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BULOG Dapat Dukungan Finansial Penuh dari Pemerintah untuk Swasembada</t>
+          <t>Sering terbangun tengah malam? Kenali 7 penyebab dan cara mengatasinya</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:54:32 +0700</t>
+          <t>Mon, 03 Aug 2026 13:35:20 +0700</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Perum BULOG mengapresiasi dukungan pemerintah dalam memperkuat perannya sebagai operator pangan nasional.</t>
+          <t>Bangun di tengah malam sesekali merupakan hal yang normal. Namun, jika kondisi ini terjadi hampir setiap malam dan ...</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8603050/bulog-dapat-dukungan-finansial-penuh-dari-pemerintah-untuk-swasembada</t>
+          <t>https://www.antaranews.com/berita/5677357/sering-terbangun-tengah-malam-kenali-7-penyebab-dan-cara-mengatasinya</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/direktur-utama-dirut-perum-bulog-letnan-jenderal-tni-purn-ahmad-rizal-ramdhani-1785768755808.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/Penumpang-rela-menginap-menunggu-kereta-pertama-di-Stasiun-Cikarang-150726-ryl-5.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bulog Jamin MBG Tak Pakai Beras SPHP dan Minyakita</t>
+          <t>Bahaya paparan pornografi pada anak: Dampak bagi otak, mental, dan perilaku</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:45:27 +0700</t>
+          <t>Mon, 03 Aug 2026 13:23:03 +0700</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Perum Bulog memastikan bahan pangan untuk program makan bergizi gratis (MBG) merupakan produk premium, bukan beras SPHP maupun Minyakita.</t>
+          <t>Perkembangan teknologi membuat anak-anak dan remaja semakin akrab dengan internet sejak usia dini. Di satu sisi, ...</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603041/bulog-jamin-mbg-tak-pakai-beras-sphp-dan-minyakita</t>
+          <t>https://www.antaranews.com/berita/5677332/bahaya-paparan-pornografi-pada-anak-dampak-bagi-otak-mental-dan-perilaku</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/29/dirut-bulog-ahmad-rizal-ramdhani-1767018144863_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/02/ilustrasi-konten-berbau-pornografi.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tawarkan Pasok Beras Berkualitas, Thailand Mau Impor Pupuk RI</t>
+          <t>Sudah ngantuk tapi sulit tidur pulas? Ini penyebab dan cara atasinya</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 21:12:37 +0700</t>
+          <t>Mon, 03 Aug 2026 11:28:54 +0700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul berharap Indonesia dan Thailand semakin mempererat kerja sama di sektor pangan.</t>
+          <t>Rasa kantuk yang muncul di malam hari seharusnya menjadi pertanda bahwa tubuh siap beristirahat. Namun, tidak sedikit ...</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603009/tawarkan-pasok-beras-berkualitas-thailand-mau-impor-pupuk-ri</t>
+          <t>https://www.antaranews.com/berita/5677203/sudah-ngantuk-tapi-sulit-tidur-pulas-ini-penyebab-dan-cara-atasinya</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891165_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/17/Nafas.jpeg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Lifestyle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BNI Hadirkan Ekosistem Keuangan Digital bagi Mahasiswa RI di Hong Kong</t>
+          <t>Cara cepat tidur dalam 5 menit, efektif untuk yang sulit pulas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:53:27 +0700</t>
+          <t>Mon, 03 Aug 2026 11:25:40 +0700</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BNI perluas layanan keuangan digital untuk mahasiswa Indonesia di Hong Kong, termasuk pembukaan rekening dan kartu debit multicurrency.</t>
+          <t>Sulit tidur meski badan sudah terasa lelah merupakan masalah yang kerap dialami banyak orang. Kondisi ini sering ...</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8602989/bni-hadirkan-ekosistem-keuangan-digital-bagi-mahasiswa-ri-di-hong-kong</t>
+          <t>https://www.antaranews.com/berita/5677199/cara-cepat-tidur-dalam-5-menit-efektif-untuk-yang-sulit-pulas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/bni-1785765055910_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/04/tidua.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tekno</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bicara Investasi, PM Thailand Ungkap Bangkok Bank Caplok Bank Permata</t>
+          <t>Cara mengganti password WiFi lewat HP dan laptop dengan mudah</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:08:33 +0700</t>
+          <t>Mon, 03 Aug 2026 13:16:14 +0700</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Presiden Prabowo Subianto menerima kunjungan Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana Kepresidenan.</t>
+          <t>WiFi yang tiba-tiba terasa lambat padahal sinyal penuh dan kuota internet masih banyak tentu membuat kesal. Salah satu ...</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/moneter/d-8602936/bicara-investasi-pm-thailand-ungkap-bangkok-bank-caplok-bank-permata</t>
+          <t>https://www.antaranews.com/berita/5677312/cara-mengganti-password-wifi-lewat-hp-dan-laptop-dengan-mudah</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891099_169.jpeg?w=360&amp;q=90</t>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/08/19/antarafoto-warga-sediakan-internet-gratis-bagi-pelajar-190820-ief-2-1.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Detik</t>
+          <t>Antara</t>
         </is>
       </c>
     </row>
@@ -786,28 +786,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Konflik Global Tekan Ekonomi Dunia, Indonesia Tetap Optimistis Tumbuh Kuat</t>
+          <t>Uji Coba Tabung CNG 3 Kg Masuk Tahap Akhir</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:00:37 +0700</t>
+          <t>Mon, 03 Aug 2026 22:58:12 +0700</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KSSK memastikan stabilitas fiskal, moneter, dan keuangan RI tetap terjaga pada triwulan II 2026 di tengah gejolak ekonomi global.</t>
+          <t>Menteri ESDM Bahlil Lahadalia menyampaikan tabung Compressed Natural Gas (CNG) 3 kilogram (kg) sebagai pengganti LPG 3 kg memasuki pengujian tahap akhir.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602771/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat</t>
+          <t>https://finance.detik.com/energi/d-8603105/uji-coba-tabung-cng-3-kg-masuk-tahap-akhir</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat-1785756837860_169.jpeg?w=360&amp;q=90</t>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/20/cadangan-gas-raksasa-ditemukan-di-kaltim-pemerintah-genjot-energi-nasional-1776674766178_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -824,38 +824,342 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Purbaya Tunggu Instruksi Prabowo soal Penyaluran DBH Rp 70 T ke Daerah</t>
+          <t>Dapat Margin Fee 7%, Bulog Targetkan Untung Rp 1,14 Triliun</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mon, 03 Aug 2026 20:00:03 +0700</t>
+          <t>Mon, 03 Aug 2026 22:32:25 +0700</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Pemerintah menetapkan margin fee untuk Perum Bulog sebesar 7%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8603085/dapat-margin-fee-7-bulog-targetkan-untung-rp-1-14-triliun</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/22/f0bc228f-67f0-4a85-b1de-c8b83e0fc898_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pemerintah Kejar Rasio Wirausaha 8 Persen pada 2045</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UMKM makanan siap saji menjadi salah satu penggerak kewirausahaan nasional. Sejalan dengan pemerintah menargetkan rasio wirausaha mencapai 8 persen pada 2045.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8602134/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045-1785739243678.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BULOG Dapat Dukungan Finansial Penuh dari Pemerintah untuk Swasembada</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:54:32 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Perum BULOG mengapresiasi dukungan pemerintah dalam memperkuat perannya sebagai operator pangan nasional.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8603050/bulog-dapat-dukungan-finansial-penuh-dari-pemerintah-untuk-swasembada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/direktur-utama-dirut-perum-bulog-letnan-jenderal-tni-purn-ahmad-rizal-ramdhani-1785768755808.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bulog Jamin MBG Tak Pakai Beras SPHP dan Minyakita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Perum Bulog memastikan bahan pangan untuk program makan bergizi gratis (MBG) merupakan produk premium, bukan beras SPHP maupun Minyakita.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603041/bulog-jamin-mbg-tak-pakai-beras-sphp-dan-minyakita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/29/dirut-bulog-ahmad-rizal-ramdhani-1767018144863_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tawarkan Pasok Beras Berkualitas, Thailand Mau Impor Pupuk RI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:12:37 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul berharap Indonesia dan Thailand semakin mempererat kerja sama di sektor pangan.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603009/tawarkan-pasok-beras-berkualitas-thailand-mau-impor-pupuk-ri</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891165_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BNI Hadirkan Ekosistem Keuangan Digital bagi Mahasiswa RI di Hong Kong</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:53:27 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BNI perluas layanan keuangan digital untuk mahasiswa Indonesia di Hong Kong, termasuk pembukaan rekening dan kartu debit multicurrency.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8602989/bni-hadirkan-ekosistem-keuangan-digital-bagi-mahasiswa-ri-di-hong-kong</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/bni-1785765055910_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bicara Investasi, PM Thailand Ungkap Bangkok Bank Caplok Bank Permata</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:08:33 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima kunjungan Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana Kepresidenan.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8602936/bicara-investasi-pm-thailand-ungkap-bangkok-bank-caplok-bank-permata</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Konflik Global Tekan Ekonomi Dunia, Indonesia Tetap Optimistis Tumbuh Kuat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:00:37 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>KSSK memastikan stabilitas fiskal, moneter, dan keuangan RI tetap terjaga pada triwulan II 2026 di tengah gejolak ekonomi global.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8602771/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat-1785756837860_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Purbaya Tunggu Instruksi Prabowo soal Penyaluran DBH Rp 70 T ke Daerah</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:00:03 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Menteri Keuangan Purbaya Yudhi Sadewa menunggu restu Presiden Prabowo Subianto untuk menyalurkan Dana Bagi Hasil (DBH) Rp 70 triliun ke Pemda.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602882/purbaya-tunggu-instruksi-prabowo-soal-penyaluran-dbh-rp-70-t-ke-daerah</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186785962_169.jpeg?w=360&amp;q=90</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Detik</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -778,388 +778,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Uji Coba Tabung CNG 3 Kg Masuk Tahap Akhir</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 22:58:12 +0700</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Menteri ESDM Bahlil Lahadalia menyampaikan tabung Compressed Natural Gas (CNG) 3 kilogram (kg) sebagai pengganti LPG 3 kg memasuki pengujian tahap akhir.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/energi/d-8603105/uji-coba-tabung-cng-3-kg-masuk-tahap-akhir</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/20/cadangan-gas-raksasa-ditemukan-di-kaltim-pemerintah-genjot-energi-nasional-1776674766178_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dapat Margin Fee 7%, Bulog Targetkan Untung Rp 1,14 Triliun</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 22:32:25 +0700</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pemerintah menetapkan margin fee untuk Perum Bulog sebesar 7%</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/industri/d-8603085/dapat-margin-fee-7-bulog-targetkan-untung-rp-1-14-triliun</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/22/f0bc228f-67f0-4a85-b1de-c8b83e0fc898_169.jpg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pemerintah Kejar Rasio Wirausaha 8 Persen pada 2045</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 22:00:05 +0700</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>UMKM makanan siap saji menjadi salah satu penggerak kewirausahaan nasional. Sejalan dengan pemerintah menargetkan rasio wirausaha mencapai 8 persen pada 2045.</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602134/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045-1785739243678.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BULOG Dapat Dukungan Finansial Penuh dari Pemerintah untuk Swasembada</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 21:54:32 +0700</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Perum BULOG mengapresiasi dukungan pemerintah dalam memperkuat perannya sebagai operator pangan nasional.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/ekonomi-bisnis/d-8603050/bulog-dapat-dukungan-finansial-penuh-dari-pemerintah-untuk-swasembada</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/direktur-utama-dirut-perum-bulog-letnan-jenderal-tni-purn-ahmad-rizal-ramdhani-1785768755808.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Bulog Jamin MBG Tak Pakai Beras SPHP dan Minyakita</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 21:45:27 +0700</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Perum Bulog memastikan bahan pangan untuk program makan bergizi gratis (MBG) merupakan produk premium, bukan beras SPHP maupun Minyakita.</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603041/bulog-jamin-mbg-tak-pakai-beras-sphp-dan-minyakita</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/29/dirut-bulog-ahmad-rizal-ramdhani-1767018144863_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tawarkan Pasok Beras Berkualitas, Thailand Mau Impor Pupuk RI</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 21:12:37 +0700</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul berharap Indonesia dan Thailand semakin mempererat kerja sama di sektor pangan.</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603009/tawarkan-pasok-beras-berkualitas-thailand-mau-impor-pupuk-ri</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891165_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BNI Hadirkan Ekosistem Keuangan Digital bagi Mahasiswa RI di Hong Kong</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 20:53:27 +0700</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>BNI perluas layanan keuangan digital untuk mahasiswa Indonesia di Hong Kong, termasuk pembukaan rekening dan kartu debit multicurrency.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/moneter/d-8602989/bni-hadirkan-ekosistem-keuangan-digital-bagi-mahasiswa-ri-di-hong-kong</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/bni-1785765055910_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Bicara Investasi, PM Thailand Ungkap Bangkok Bank Caplok Bank Permata</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 20:08:33 +0700</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Presiden Prabowo Subianto menerima kunjungan Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana Kepresidenan.</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/moneter/d-8602936/bicara-investasi-pm-thailand-ungkap-bangkok-bank-caplok-bank-permata</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891099_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Konflik Global Tekan Ekonomi Dunia, Indonesia Tetap Optimistis Tumbuh Kuat</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 20:00:37 +0700</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>KSSK memastikan stabilitas fiskal, moneter, dan keuangan RI tetap terjaga pada triwulan II 2026 di tengah gejolak ekonomi global.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/foto-bisnis/d-8602771/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/konflik-global-tekan-ekonomi-dunia-indonesia-tetap-optimistis-tumbuh-kuat-1785756837860_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Purbaya Tunggu Instruksi Prabowo soal Penyaluran DBH Rp 70 T ke Daerah</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Mon, 03 Aug 2026 20:00:03 +0700</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Menteri Keuangan Purbaya Yudhi Sadewa menunggu restu Presiden Prabowo Subianto untuk menyalurkan Dana Bagi Hasil (DBH) Rp 70 triliun ke Pemda.</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8602882/purbaya-tunggu-instruksi-prabowo-soal-penyaluran-dbh-rp-70-t-ke-daerah</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/purbaya-tak-bisa-tidur-jelang-tutup-buku-apbn-2025-1767186785962_169.jpeg?w=360&amp;q=90</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Detik</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -778,8 +778,312 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Uji Coba Tabung CNG 3 Kg Masuk Tahap Akhir</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:58:12 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia menyampaikan tabung Compressed Natural Gas (CNG) 3 kilogram (kg) sebagai pengganti LPG 3 kg memasuki pengujian tahap akhir.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8603105/uji-coba-tabung-cng-3-kg-masuk-tahap-akhir</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/20/cadangan-gas-raksasa-ditemukan-di-kaltim-pemerintah-genjot-energi-nasional-1776674766178_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dapat Margin Fee 7%, Bulog Targetkan Untung Rp 1,14 Triliun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:32:25 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pemerintah menetapkan margin fee untuk Perum Bulog sebesar 7%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8603085/dapat-margin-fee-7-bulog-targetkan-untung-rp-1-14-triliun</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/02/22/f0bc228f-67f0-4a85-b1de-c8b83e0fc898_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pemerintah Kejar Rasio Wirausaha 8 Persen pada 2045</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:00:05 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>UMKM makanan siap saji menjadi salah satu penggerak kewirausahaan nasional. Sejalan dengan pemerintah menargetkan rasio wirausaha mencapai 8 persen pada 2045.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8602134/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/pemerintah-kejar-rasio-wirausaha-8-persen-pada-2045-1785739243678.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BULOG Dapat Dukungan Finansial Penuh dari Pemerintah untuk Swasembada</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:54:32 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Perum BULOG mengapresiasi dukungan pemerintah dalam memperkuat perannya sebagai operator pangan nasional.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/ekonomi-bisnis/d-8603050/bulog-dapat-dukungan-finansial-penuh-dari-pemerintah-untuk-swasembada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/direktur-utama-dirut-perum-bulog-letnan-jenderal-tni-purn-ahmad-rizal-ramdhani-1785768755808.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bulog Jamin MBG Tak Pakai Beras SPHP dan Minyakita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:45:27 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Perum Bulog memastikan bahan pangan untuk program makan bergizi gratis (MBG) merupakan produk premium, bukan beras SPHP maupun Minyakita.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603041/bulog-jamin-mbg-tak-pakai-beras-sphp-dan-minyakita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/29/dirut-bulog-ahmad-rizal-ramdhani-1767018144863_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tawarkan Pasok Beras Berkualitas, Thailand Mau Impor Pupuk RI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:12:37 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Perdana Menteri (PM) Thailand Anutin Charnvirakul berharap Indonesia dan Thailand semakin mempererat kerja sama di sektor pangan.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8603009/tawarkan-pasok-beras-berkualitas-thailand-mau-impor-pupuk-ri</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891165_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BNI Hadirkan Ekosistem Keuangan Digital bagi Mahasiswa RI di Hong Kong</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:53:27 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BNI perluas layanan keuangan digital untuk mahasiswa Indonesia di Hong Kong, termasuk pembukaan rekening dan kartu debit multicurrency.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8602989/bni-hadirkan-ekosistem-keuangan-digital-bagi-mahasiswa-ri-di-hong-kong</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/bni-1785765055910_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bicara Investasi, PM Thailand Ungkap Bangkok Bank Caplok Bank Permata</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:08:33 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menerima kunjungan Perdana Menteri (PM) Thailand Anutin Charnvirakul di Istana Kepresidenan.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8602936/bicara-investasi-pm-thailand-ungkap-bangkok-bank-caplok-bank-permata</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/prabowo-terima-kunjungan-pm-thailand-kerja-sama-bilateral-makin-diperkuat-1785753891099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H9"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$H$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,7 @@
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +474,11 @@
           <t>Media</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Sentimen</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,6 +517,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +556,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -587,6 +595,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +634,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -663,6 +673,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,6 +712,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -739,6 +751,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -777,6 +790,7 @@
           <t>Antara</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -815,6 +829,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -853,6 +868,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -891,6 +907,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -929,6 +946,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -967,6 +985,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1005,6 +1024,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1043,6 +1063,7 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1081,9 +1102,10 @@
           <t>Detik</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H17"/>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,18 +419,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,8 +856,1136 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VinFast VF MPV 7, Standar Baru Kenyamanan Mobil Listrik Keluarga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:10:59 +0700</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VinFast VF MPV 7, MPV listrik terluas di Indonesia, menawarkan kenyamanan, efisiensi biaya, dan performa impresif. Solusi ideal untuk keluarga modern.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803220721-37-756242/vinfast-vf-mpv-7-standar-baru-kenyamanan-mobil-listrik-keluarga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/vinfast-vf-mpv-7-ditampilkan-dalam-acara-giias-2026-di-ice-bsd-city-kabupaten-tangerang-banten-rabu-2972026-1785309136237_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Terungkap, Senjata Super Canggih China Ternyata Buatan Amerika</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Lembaga riset militer China memanfaatkan AI buatan AS untuk meningkatkan senjata militer. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803143903-37-756101/terungkap-senjata-super-canggih-china-ternyata-buatan-amerika</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/12/02/bendera-amerikas-serikat-as-dan-china-reutersflorence-loillustrationfile_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Viral Rekam Wanita Tanpa Izin Pakai Kacamata, Ini Kata Menkomdigi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Viral kasus perekaman usher di GIIAS 2026 tanpa izin. Menteri Komdigi menegaskan pelanggaran UU PDP dan etika. Tindakan serius akan diambil pemerintah.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803173516-37-756196/viral-rekam-wanita-tanpa-izin-pakai-kacamata-ini-kata-menkomdigi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/01/ray-ban-meta-blayzer-optics-gen-2-1775020577848_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ada Rokok Vape di Konten Anak, Menkomdigi Bilang YouTube Tak Konsisten</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 20:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti Dewi</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kementerian Komunikasi dan Digital memanggil YouTube terkait pelanggaran konten vape.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803174122-37-756203/ada-rokok-vape-di-konten-anak-menkomdigi-bilang-youtube-tak-konsisten</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-komunikasi-dan-digital-meutya-hafid-di-kantor-komdigi-senin-382026-1785753783845_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Aturan RI Gagal di Australia, Warga Sudah Kecanduan Parah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:35:10 +0700</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pemerintah Australia membela larangan media sosial untuk anak di bawah 16 tahun, meski data menunjukkan banyak remaja tetap menggunakannya.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803192211-37-756223/aturan-ri-gagal-di-australia-warga-sudah-kecanduan-parah</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/26/ilustrasi-sosial-media-reutershollie-adamsillustrationfile-photo-1782443076696_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dunia Dalam Bahaya Besar Gara-Gara Amerika, Eropa Langsung Bertindak</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Regulator Eropa panggil OpenAI dan Anthropic setelah insiden AI fatal. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803150909-37-756132/dunia-dalam-bahaya-besar-gara-gara-amerika-eropa-langsung-bertindak</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/12/foto-kolase-ceo-openai-sam-altman-dan-ceo-anthropic-dario-amodei-1781242685458_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>XL Pamer Jaringan 5G, Beberkan Bukti Internet Paling Ngebut</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>XL menjadi pemimpin jaringan 5G di Indonesia, meraih penghargaan Best Mobile Network dan tiga kategori 5G dari Ookla.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803180348-37-756210/xl-pamer-jaringan-5g-beberkan-bukti-internet-paling-ngebut</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/21/ilustrasi-xlsmart-cnbc-indonesiafaisal-rahman-1745222330387_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kunang-Kunang Hilang Satu per Satu, Ahli IPB Ungkap Tanda Petaka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kunang-kunang makin langka di Indonesia, menjadi indikator kesehatan ekosistem. Simak penjelasan ahli IPB!</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803142624-37-756097/kunang-kunang-hilang-satu-per-satu-ahli-ipb-ungkap-tanda-petaka</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/25/hewan-kunang-kunang-1782356753360_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fitur Baru Google Jadi Sorotan, Baru Sehari Langsung Diblokir</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Google menangguhkan fitur AI di Google Earth setelah kritik terkait potensi disinformasi. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803141046-37-756091/fitur-baru-google-jadi-sorotan-baru-sehari-langsung-diblokir</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/15/google-flight-simulator-1781507395607_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cara Manusia Rp 3.000 Triliun Hadapi Petaka Baru yang Mengancam Dunia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Nvidia membentuk 'Open Secure AI Alliance' untuk meningkatkan keamanan AI setelah insiden peretasan oleh agen AI.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803132549-37-756065/cara-manusia-rp-3000-triliun-hadapi-petaka-baru-yang-mengancam-dunia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/18/jaket-kulit-milik-ceo-nvidia-jensen-huang-terjual-di-pelelangan-seharga-us960000-atau-sekitar-rp17-miliar-salah-satu-jaket-kul-1784364904256_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Terungkap Taktik China Mata-Matai Warga Dunia 24 Jam Penuh</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Temuan mengejutkan mengungkap pengawasan China terhadap warga asing, termasuk turis dan jurnalis. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803123352-37-756030/terungkap-taktik-china-mata-matai-warga-dunia-24-jam-penuh</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/08/04/65edf635-3fec-4fc9-ad03-588d3c52e1e1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6 Langkah yang Harus Dilakukan Jika HP Hilang Biar Rekening Aman</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti Dewi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kehilangan HP bukan hanya kehilangan perangkat. Lindungi data pribadi dengan 6 langkah penting, termasuk memblokir SIM dan ganti kata sandi email.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803122412-37-756026/6-langkah-yang-harus-dilakukan-jika-hp-hilang-biar-rekening-aman</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/08/handphone-dan-barang-elektronik-bekas-di-pasar-loak-jatinegara-jakarta-timur-cnbc-indonesiaintan-1759908166554_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tanda Krisis iPhone Tiba, Uang Rp 8.000 Triliun Bisa Hilang Seketika</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Krisis kelangkaan chip memori global memengaruhi industri smartphone, tak terkecuali perusahaan kawakan seperti Apple. Simak!</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803121528-37-756024/tanda-krisis-iphone-tiba-uang-rp-8000-triliun-bisa-hilang-seketika</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/17/calon-pembeli-melihat-iphone-17-series-di-gerai-ibox-kota-kasablanka-jakarta-jumat-17102025-cnbc-indonesiafaisal-rahman-1760684676968_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Laptop Apple Paling Laku Tiba-Tiba Hilang, Naik Harga Gila-gilaan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kelangkaan chip memori global mengganggu pasokan MacBook Air Apple, menyebabkan kenaikan harga dan keterlambatan pengiriman.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803120328-37-756018/laptop-apple-paling-laku-tiba-tiba-hilang-naik-harga-gila-gilaan</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/06/07/seorang-peserta-mengambil-gambar-laptop-macbook-air-yang-baru-didesain-ulang-selama-wwdc22-di-apple-park-pada-06-juni-2022-di-_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Amerika Bawa Petaka Baru, Waspada Satu Dunia Bisa Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Insiden berbahaya terkait AI canggih meningkat, termasuk pelanggaran oleh OpenAI dan Anthropic. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803114755-37-756012/amerika-bawa-petaka-baru-waspada-satu-dunia-bisa-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/presiden-donald-trump-berbicara-di-upacara-pemakaman-senator-lindsey-graham-r-sc-di-katedral-nasional-washington-selasa-28-jul-1785285528470_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Malaysia Mendadak Tutup 'Sekolah' Orang Kaya, Ternyata Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pemerintah Malaysia menutup Network School, komunitas startup yang didirikan pengusaha kaya Balaji Srinivasan.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803113625-37-756001/malaysia-mendadak-tutup-sekolah-orang-kaya-ternyata-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/balaji-s-srinivasan-1785732039847_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Video Call di WhatsApp Web Berubah Mirip Zoom, Begini Caranya</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WhatsApp Web kini mendukung panggilan suara dan video tanpa aplikasi tambahan. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803112442-37-755997/video-call-di-whatsapp-web-berubah-mirip-zoom-begini-caranya</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/07/26/2bdfd888-1b1c-404d-a284-71aa1c14308d_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Aplikasi Google Sedot Baterai HP, Ini Daftar dan Cara Menanggulanginya</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Baterai smartphone boros? Temukan aplikasi Google yang menguras daya, seperti YouTube, Chrome, dan Maps. Simak tips menghemat baterai!</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803111726-37-755985/aplikasi-google-sedot-baterai-hp-ini-daftar-dan-cara-menanggulanginya</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/03/12/875b1aa9-f40b-49a9-9e22-fb1f02cbb6d3_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Menkomdigi Tegur YouTube Soal Jualan Vape di Acara Anak-Anak</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kementerian Komunikasi menegur YouTube atas promosi vape pada anak di siaran langsung.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803095709-37-755943/menkomdigi-tegur-youtube-soal-jualan-vape-di-acara-anak-anak</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/26/menteri-komunikasi-dan-digital-meutya-hafid-saat-mengunjungi-pameran-foto-jurnalistik-antara-bertema-perisai-tunas-di-antara-h-1782465656989_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nasib Karyawan Google, Tim Menang Nobel Malah Dibubarkan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Google membubarkan tim AlphaFold DeepMind dua tahun setelah dua ilmuwan meraih Nobel Kimia.</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803095320-37-755939/nasib-karyawan-google-tim-menang-nobel-malah-dibubarkan</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/01/30/5282957a-ad03-44f2-a2c5-387f6dcb1f7a_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sedekade CICIL: Rayakan Transformasi-Komitmen Dukung Sektor Produktif</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:08:39 +0700</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CICIL merayakan satu dekade transformasi dengan tema "A Decade of Growth". Fokus pada inklusi keuangan dan dukungan sektor produktif di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803090241-37-755921/sedekade-cicil-rayakan-transformasi-komitmen-dukung-sektor-produktif</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/direktur-cicil-oki-surya-dok-cicil-1785722899263_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Roket Elon Musk Akan Menabrak Bulan Kamis Pagi</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 08:35:48 +0700</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Potongan roket Falcon 9 SpaceX diperkirakan menabrak Bulan pada 5 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803083300-37-755913/roket-elon-musk-akan-menabrak-bulan-kamis-pagi</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/13/roket-spacex-falcon-9-dan-pesawat-ruang-angkasa-dragon-lepas-landas-dalam-misi-crew-12-nasa-ke-stasiun-luar-angkasa-internasio-1770990649397_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pemilik Tesla Dibayangi Bahaya, Dibongkar Mantan Karyawan Elon Musk</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Javier Medrano, menggugat perusahaan karena kurangnya pengawasan fitur full self-driving yang berpotensi membahayakan keselamatan.</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803060808-37-755876/pemilik-tesla-dibayangi-bahaya-dibongkar-mantan-karyawan-elon-musk</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/08/mobil-model-y-standard-dari-tesla-motors-terlihat-dalam-gambar-selebaran-yang-dirilis-oleh-tesla-motors-pada-tanggal-7-oktober-1759894895986_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pemilik Telegram Diburu Anak Buah Vladimir Putin</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Rusia memburu bos Telegram, Pavel Durov, karena dituduh memfasilitasi terorisme. Durov kini berbasis di Dubai, dan keberadaannya tidak jelas.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260803060445-37-755875/pemilik-telegram-diburu-anak-buah-vladimir-putin</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/02/03/85087159-ecdf-4c2f-8ebc-55bcf4dd7784_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
+  <autoFilter ref="A1:I33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,13 +419,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
@@ -1984,8 +1984,1136 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tangis Keluarga Pecah Lepas Kepergian Diding Boneng Selamanya</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 22:02:40 +0700</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aktor Zainal Abidin, dikenal sebagai Diding Boneng, dimakamkan di TPU Menteng Pulo. Keluarga dan pelayat berduka atas kepergiannya yang mendadak.</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602853/tangis-keluarga-pecah-lepas-kepergian-diding-boneng-selamanya</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/diding-boneng-1785753423952_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Momen Manis Atiqah Hasiholan dan Anak Temani Rio Dewanto Fashion Show</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 21:02:44 +0700</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Atiqah Hasiholan berbagi momen seru. Ia bersama anaknya menemani Rio Dewanto kerja.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601877/momen-manis-atiqah-hasiholan-dan-anak-temani-rio-dewanto-fashion-show</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/rio-dewanto-1785730235838_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Model Cilik Sienna Simanjuntak Tampil Warna-warni di Indonesia Fashion Week 2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:39:31 +0700</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Atmi Ahsani Yusron</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Model cilik Sienna Valencia tampil memukau di Indonesia Fashion Week 2026 dengan dua busana berwarna-warni. Dia menunjukkan semangat positif untuk anak-anak.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602883/model-cilik-sienna-simanjuntak-tampil-warna-warni-di-indonesia-fashion-week-2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/sienna-valencia-simanjuntak-1785759829113.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gilang Dirga Termotivasi Jadi Sarjana Usai Istri Lulus Setelah 18 Tahun Kuliah</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:09:05 +0700</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Adiezty Fersa lulus setelah 18 tahun kuliah. Gilang Dirga termotivasi untuk melanjutkan kuliah.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602051/gilang-dirga-termotivasi-jadi-sarjana-usai-istri-lulus-setelah-18-tahun-kuliah</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/26/gilang-dirga-1782446955856_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Raisya Brazuca Happy Jadi Artis Mak Vera, Langsung Dapat Proyek Film</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:08:21 +0700</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Raisya Brazuca, model dan pemain sinetron berusia 12 tahun, bergabung dengan manajemen Mak Vera. Ia siap memerankan tokoh utama dalam film Bendera Buat Asiang.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602807/raisya-brazuca-happy-jadi-artis-mak-vera-langsung-dapat-proyek-film</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/raisya-brazuca-1785758222929_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pihak Ruben Onsu Tegaskan Hasil Tes Kesehatan</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 19:04:14 +0700</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Ruben Onsu, Minola Sebayang, klarifikasi isu kesehatan kliennya terkait rumor HIV. Hasil pemeriksaan menunjukkan status non-reaktif.</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602809/pihak-ruben-onsu-tegaskan-hasil-tes-kesehatan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/22/ruben-onsu-1784693461329_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Selamat Jalan, Diding Boneng</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 18:00:54 +0700</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia pada Senin, 3 Agustus 2026. Pemilik nama lengkap Zainal Abidin tersebut, dimakamkan di TPU Menteng Pulo, Jakarta.</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602700/selamat-jalan-diding-boneng</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/diding-boneng-1785753424045_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sehat Sekaligus Habiskan Waktu Bareng ala Anji dan Istri</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 17:07:56 +0700</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Penyanyi Anji bareng istrinya, Dena Desy, mengikuti kompetisi lari. Begini momennya.</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601968/sehat-sekaligus-habiskan-waktu-bareng-ala-anji-dan-istri</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/anji-1785733421654_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kimberly Ryder Rahasiakan Sosok Pacar demi Jaga Privasi</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 16:06:49 +0700</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kimberly Ryder lebih selektif membagikan kehidupan pribadinya, terutama soal asmara. Ia menjaga privasi kekasih barunya.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602452/kimberly-ryder-rahasiakan-sosok-pacar-demi-jaga-privasi</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/06/kimberly-ryder-1759738119166_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Momen Bahagia Joanna Alexandra dan Immanuel Christover di Resepsi Pernikahan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 15:09:58 +0700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Immanuel Christover dan Joanna Alexandra menggelar pernikahan intimate di hotel berbintang. Ini momen bahagia mereka.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602366/momen-bahagia-joanna-alexandra-dan-immanuel-christover-di-resepsi-pernikahan</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/joanna-aklexandra-1785743358499_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kondisi Terakhir Diding Boneng Sebelum Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 14:12:16 +0700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aktor Diding Boneng meninggal dunia pada 3 Agustus 2026. Keluarga mengungkapkan perjuangannya melawan stroke dan kondisi kesehatan yang menurun.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602057/kondisi-terakhir-diding-boneng-sebelum-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/diding-bonengsekar-aqillah-indraswari-1767171128160_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sambut HUT RI ke-81, Reyhan &amp;amp; Rafie Rilis Lagu Patriotik Kita Satu Indonesia</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:15:31 +0700</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Duo kakak-beradik Reyhan dan Rafie luncurkan lagu patriotik Kita Satu Indonesia untuk rayakan Hari Kemerdekaan RI ke-81, ajak persatuan di tengah keberagaman.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8602079/sambut-hut-ri-ke-81-reyhan-rafie-rilis-lagu-patriotik-kita-satu-indonesia</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/reyhan-rafie-1785737425322_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Suasana Duka di Rumah Diding Boneng</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 13:05:22 +0700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ahs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia pada Senin (3/8/2026) pagi. Ini suasana duka di rumah Diding Boneng.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8602011/suasana-duka-di-rumah-diding-boneng</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/diding-boneng-1785732521105_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Kronologi Diding Boneng Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 12:30:21 +0700</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aktor Diding Boneng meninggal dunia pada 3 Agustus 2026 setelah berjuang melawan stroke dan komplikasi kesehatan lainnya. Jenazah disemayamkan di rumah duka.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601962/kronologi-diding-boneng-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/21/diding-boneng-1771648910866_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Rumah Duka Diding Boneng Dipadati Pelayat</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:58:08 +0700</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Dunia hiburan berduka, aktor Diding Boneng meninggal dunia pada 3 Agustus 2026. Jenazahnya disemayamkan di rumah duka sebelum dimakamkan di TPU Menteng Pulo.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601948/rumah-duka-diding-boneng-dipadati-pelayat</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/diding-boneng-1785732521105_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Zack Lee dan Indri AFI, Ada Apa Nih?</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:25:26 +0700</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Wajah Zack Lee muncul dalam unggahan media sosial Indri AFI. Kedekatan mereka bikin penasaran netizen. Ada apa nih?</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601704/zack-lee-dan-indri-afi-ada-apa-nih</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/03/zack-lee-dan-indri-afi-1785720914368_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Erika Carlina Soal Peluang Punya Pasangan Lagi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 11:01:41 +0700</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Erika Carlina berbicara tentang masa depannya sebagai single mom. Dia fokus membesarkan anaknya, Andrew, dan menyerahkan urusan jodoh kepada Tuhan.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601431/erika-carlina-soal-peluang-punya-pasangan-lagi</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/10/erika-carlina-1778412291280_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Diding Boneng Akan Dimakamkan di TPU Menteng Pulo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 10:01:21 +0700</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia pada usia 76 tahun. Pemakaman dijadwalkan di Menteng Pulo.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601740/diding-boneng-akan-dimakamkan-di-tpu-menteng-pulo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/30/diding-boneng-1767068239561_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Kabar Duka, Diding Boneng Meninggal Dunia</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:12:35 +0700</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aktor senior Diding Boneng meninggal dunia pada usia 76 tahun.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601677/kabar-duka-diding-boneng-meninggal-dunia</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/30/diding-boneng-1767068239739_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Erika Carlina Lebih Tenang-Sabar Usai Jadi Ibu</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 09:09:13 +0700</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aktris Erika Carlina berbagi perubahan hidup setelah menjadi ibu. Kehadiran putranya, Andrew, membawanya ke arah yang lebih baik dan tenang.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601329/erika-carlina-lebih-tenang-sabar-usai-jadi-ibu</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/25/erika-carlina-1766630146631_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Rey Mbayang Nikmati Pendakian Gunung Merbabu, Makin Cantik Ada Dinda Hauw</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 08:08:38 +0700</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Rey Mbayang dan Dinda Hauw beberapa waktu lalu melakukan pendakian ke Gunung Merbabu. Rey Mbayang bahagia menikmati keindahannya.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601410/rey-mbayang-nikmati-pendakian-gunung-merbabu-makin-cantik-ada-dinda-hauw</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/rey-mbayang-1785674920731_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Detik-detik Anak Erika Carlina Pertama Kali Melangkah</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:07:01 +0700</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Anak Erika Carlina, Andrew Raxy Neil, memperlihatkan pertama kali melangkah.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601206/detik-detik-anak-erika-carlina-pertama-kali-melangkah</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/erika-carlina-1785663019867_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Selamat! Joanna Alexandra Nikah dengan Immanuel Christover</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 06:06:57 +0700</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Joanna Alexandra melepas status janda. Ia dan Immanuel Christover resmi menikah.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601519/selamat-joanna-alexandra-nikah-dengan-immanuel-christover</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/joanna-alexandra-1785680233879_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ruben Onsu dan Sarwendah 'Panas' Lagi</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 05:05:35 +0700</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ruben Onsu dan Sarwendah 'panas' lagi di media sosial. Hal ini bermula ketika Sarwendah menjadi bintang tamu di channel YouTube Denny Sumargo.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8601187/ruben-onsu-dan-sarwendah-panas-lagi</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/ruben-onsu-1784843256785_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I33"/>
+  <autoFilter ref="A1:I57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-03.xlsx
+++ b/data/berita_2026-08-03.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,10 +419,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
@@ -3112,8 +3112,55 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Malaysia Selidiki Pilot Penyelundup Narkoba ke RI Bisa Lolos di KLIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 23:43:03 +0700</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pilot Malaysia ditangkap di Indonesia karena menyelundupkan 26 kg narkoba. Investigasi mendalam dilakukan terkait kelolosan pemeriksaan di bandara.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260803231914-106-1388224/malaysia-selidiki-pilot-penyelundup-narkoba-ke-ri-bisa-lolos-di-klia</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/pilot-maskapai-asing-asal-malaysia-mohd-saufi-bin-othman-mso-ditangkap-tim-gabungan-bareskrim-polri-dan-bea-cukai-bandara-soek-1785826709010_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I57"/>
+  <autoFilter ref="A1:I58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>